--- a/public/templates/template-guru.xlsx
+++ b/public/templates/template-guru.xlsx
@@ -1935,7 +1935,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C205">
-      <formula1>"guru,admin"</formula1>
+      <formula1>"guru,guru bidang,admin"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
